--- a/data/trans_dic/P25D_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25D_R-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente cigarrillos electrónicos</t>
+          <t>Población que fuma diariamente cigarrillos electrónicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,4</t>
+          <t>0,16; 1,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,61</t>
+          <t>0,07; 0,54</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 1,79</t>
+          <t>0,57; 1,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,33</t>
+          <t>0,41; 1,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,32</t>
+          <t>0,58; 1,33</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,45</t>
+          <t>0,78; 3,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,99</t>
+          <t>0,57; 1,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,15</t>
+          <t>0,85; 2,26</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,62</t>
+          <t>0,68; 1,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,43; 0,99</t>
+          <t>0,42; 0,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,18</t>
+          <t>0,62; 1,13</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente cigarrillos electrónicos</t>
+          <t>Población que fuma diariamente cigarrillos electrónicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>817; 7198</t>
+          <t>811; 7545</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1016</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>831; 7728</t>
+          <t>830; 6824</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12146; 40774</t>
+          <t>12939; 42598</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9142; 29660</t>
+          <t>9100; 29222</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26406; 59508</t>
+          <t>26041; 60076</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5317; 22237</t>
+          <t>5005; 20209</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3837; 13159</t>
+          <t>3767; 12914</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11163; 28039</t>
+          <t>11095; 29505</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23694; 55899</t>
+          <t>23422; 56074</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15843; 36046</t>
+          <t>15293; 35587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44544; 83926</t>
+          <t>43864; 80124</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25D_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P25D_R-Estudios-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,47</t>
+          <t>0,15; 1,46</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,07; 0,54</t>
+          <t>0,06; 0,63</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,87</t>
+          <t>0,78; 2,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,31</t>
+          <t>0,48; 1,33</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 1,33</t>
+          <t>0,71; 1,51</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,14</t>
+          <t>0,78; 2,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 1,96</t>
+          <t>0,56; 1,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,26</t>
+          <t>0,86; 2,08</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,63</t>
+          <t>0,82; 1,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,98</t>
+          <t>0,47; 1,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,13</t>
+          <t>0,71; 1,24</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2901</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2650</t>
+          <t>2901</t>
         </is>
       </c>
     </row>
@@ -879,7 +879,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>811; 7545</t>
+          <t>893; 8451</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>830; 6824</t>
+          <t>901; 8744</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>23797</t>
+          <t>28257</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>17690</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40243</t>
+          <t>45947</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12939; 42598</t>
+          <t>17400; 45534</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9100; 29222</t>
+          <t>10357; 28887</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26041; 60076</t>
+          <t>31055; 66371</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>11449</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7294</t>
+          <t>8254</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18259</t>
+          <t>19703</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5005; 20209</t>
+          <t>5558; 20860</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3767; 12914</t>
+          <t>4087; 14087</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11095; 29505</t>
+          <t>12345; 30083</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23422; 56074</t>
+          <t>28873; 63540</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15293; 35587</t>
+          <t>17394; 39096</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>43864; 80124</t>
+          <t>51346; 89534</t>
         </is>
       </c>
     </row>
